--- a/Data/DSP Site Expense.xlsx
+++ b/Data/DSP Site Expense.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/DSP Site Podanur/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{298DB9F6-6E70-448D-95FD-3824A09B3D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FF63FA9-F8B0-4A9A-9EAA-7BFC47BE77EC}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:1_{298DB9F6-6E70-448D-95FD-3824A09B3D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1552CA8E-7343-4069-A33C-4F4FA5F6608A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="177">
   <si>
     <t>DATE</t>
   </si>
@@ -121,9 +121,6 @@
     <t>CENTRING LABOUR</t>
   </si>
   <si>
-    <t>ELECTRICIAL LABOUR</t>
-  </si>
-  <si>
     <t>PLUMBING LABOUR</t>
   </si>
   <si>
@@ -482,6 +479,102 @@
   </si>
   <si>
     <t>Elevation Bal Amount</t>
+  </si>
+  <si>
+    <t>Muttu and Palagai Shifting Nithish</t>
+  </si>
+  <si>
+    <t>Cuttimng Blade Nithish</t>
+  </si>
+  <si>
+    <t>Nails Purchase Nithish</t>
+  </si>
+  <si>
+    <t>Cutting Blade</t>
+  </si>
+  <si>
+    <t>Lab Transport fro Echanari</t>
+  </si>
+  <si>
+    <t>Palagai from Echanari Nithish</t>
+  </si>
+  <si>
+    <t>Binding Wire 10 KG</t>
+  </si>
+  <si>
+    <t>Roof materials Adv</t>
+  </si>
+  <si>
+    <t>TSK - CHIT</t>
+  </si>
+  <si>
+    <t>Month 1</t>
+  </si>
+  <si>
+    <t>Fitter lab adv</t>
+  </si>
+  <si>
+    <t>Car Diesel</t>
+  </si>
+  <si>
+    <t>Krishna moorthy Lab</t>
+  </si>
+  <si>
+    <t>Ramesh Fitter Lab</t>
+  </si>
+  <si>
+    <t>Kannan Anbu Extra</t>
+  </si>
+  <si>
+    <t>Chakra Part payment</t>
+  </si>
+  <si>
+    <t>ELECTRICAL LABOUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roof concrete pipe work </t>
+  </si>
+  <si>
+    <t>Fitter Lab Payment roof work</t>
+  </si>
+  <si>
+    <t>Kannan Anbu Extra(500+1050)</t>
+  </si>
+  <si>
+    <t>Roof Concrete</t>
+  </si>
+  <si>
+    <t>Hook for roof to Selvam</t>
+  </si>
+  <si>
+    <t>Concrete Group Tea Roof</t>
+  </si>
+  <si>
+    <t>Roof Materials Adv</t>
+  </si>
+  <si>
+    <t>Roof part Payment</t>
+  </si>
+  <si>
+    <t>Sakku for Curing</t>
+  </si>
+  <si>
+    <t>Selvam Roof work n Concrete</t>
+  </si>
+  <si>
+    <t>Ramesh Petrol</t>
+  </si>
+  <si>
+    <t>Fitter Lab</t>
+  </si>
+  <si>
+    <t>Azhagiri Concret</t>
+  </si>
+  <si>
+    <t>Krishna - 1 L cheque from School</t>
+  </si>
+  <si>
+    <t>Cheque from School 2L</t>
   </si>
 </sst>
 </file>
@@ -547,7 +640,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,7 +672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -607,13 +700,12 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -733,7 +825,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TAMIL" refreshedDate="46148.547196643522" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="246" xr:uid="{ECDDBE9B-8132-48D6-AEC8-4A5EB49DBA77}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:D1007" sheet="Expenses"/>
+    <worksheetSource ref="A1:D1008" sheet="Expenses"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="DATE" numFmtId="164">
@@ -2264,7 +2356,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -2672,11 +2764,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB5C11F-65B6-47E4-A16E-DE6C6AA0FB0E}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.36328125" customWidth="1"/>
@@ -2688,11 +2780,11 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2701,96 +2793,130 @@
         <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K1" s="8">
         <f>SUM(B2:B99)</f>
-        <v>2000000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>46064</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="25">
         <v>300000</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>46095</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="25">
         <v>50000</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>46097</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="25">
         <v>50000</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>46129</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="25">
         <v>1500000</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>46151</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="25">
         <v>100000</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B7" s="25">
+        <v>200000</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B8" s="25">
+        <v>400000</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2800,7 +2926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}">
-  <dimension ref="A1:L305"/>
+  <dimension ref="A1:L306"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
@@ -2835,7 +2961,7 @@
       </c>
       <c r="J1" s="7">
         <f>'Payment Received'!K1</f>
-        <v>2000000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -2849,14 +2975,14 @@
         <v>1150</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="J2" s="7">
-        <f>SUM(C2:C508)</f>
-        <v>1659086</v>
+        <f>SUM(C2:C509)</f>
+        <v>2321891</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -2870,14 +2996,14 @@
         <v>2750</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="7">
         <f>J1-J2</f>
-        <v>340914</v>
+        <v>278109</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -2891,7 +3017,7 @@
         <v>300</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K4" s="17"/>
       <c r="L4" s="8"/>
@@ -2907,7 +3033,7 @@
         <v>149400</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -2921,7 +3047,7 @@
         <v>1500</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -2929,13 +3055,13 @@
         <v>46069</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="7">
         <v>200</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -2943,13 +3069,13 @@
         <v>46070</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="7">
         <v>500</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -2963,7 +3089,7 @@
         <v>2000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -2971,13 +3097,13 @@
         <v>46073</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="7">
         <v>10500</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" s="8"/>
     </row>
@@ -2986,13 +3112,13 @@
         <v>46073</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="7">
         <v>110</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -3006,7 +3132,7 @@
         <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -3020,7 +3146,7 @@
         <v>3150</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -3034,7 +3160,7 @@
         <v>5500</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -3048,7 +3174,7 @@
         <v>11400</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -3062,7 +3188,7 @@
         <v>4500</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -3076,7 +3202,7 @@
         <v>245</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I17" s="8"/>
     </row>
@@ -3091,7 +3217,7 @@
         <v>13750</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -3099,13 +3225,13 @@
         <v>46074</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="7">
         <v>5000</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -3113,13 +3239,13 @@
         <v>46074</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="7">
         <v>200</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -3127,13 +3253,13 @@
         <v>46074</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="7">
         <v>200</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -3141,13 +3267,13 @@
         <v>46076</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="7">
         <v>1000</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -3155,13 +3281,13 @@
         <v>46077</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="7">
         <v>500</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -3169,13 +3295,13 @@
         <v>46078</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="7">
         <v>630</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -3189,7 +3315,7 @@
         <v>3000</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -3197,13 +3323,13 @@
         <v>46080</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="7">
         <v>680</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -3217,7 +3343,7 @@
         <v>29800</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -3231,7 +3357,7 @@
         <v>13850</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -3245,7 +3371,7 @@
         <v>17000</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -3259,7 +3385,7 @@
         <v>2000</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -3273,7 +3399,7 @@
         <v>9600</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -3287,7 +3413,7 @@
         <v>20000</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -3301,7 +3427,7 @@
         <v>60000</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -3315,7 +3441,7 @@
         <v>50</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -3329,7 +3455,7 @@
         <v>5000</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -3337,13 +3463,13 @@
         <v>46093</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="7">
         <v>5500</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -3357,7 +3483,7 @@
         <v>5000</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -3371,7 +3497,7 @@
         <v>10000</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -3385,7 +3511,7 @@
         <v>20000</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -3393,13 +3519,13 @@
         <v>46098</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="7">
         <v>950</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -3407,13 +3533,13 @@
         <v>46098</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" s="7">
         <v>1500</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -3421,13 +3547,13 @@
         <v>46099</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C42" s="7">
         <v>400</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -3441,7 +3567,7 @@
         <v>540</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -3449,13 +3575,13 @@
         <v>46099</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C44" s="7">
         <v>300</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -3469,7 +3595,7 @@
         <v>630</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -3477,13 +3603,13 @@
         <v>46099</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" s="7">
         <v>760</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -3497,7 +3623,7 @@
         <v>5000</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -3511,7 +3637,7 @@
         <v>31400</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -3525,7 +3651,7 @@
         <v>9500</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -3539,7 +3665,7 @@
         <v>14000</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -3553,7 +3679,7 @@
         <v>150000</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -3567,7 +3693,7 @@
         <v>50000</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -3581,7 +3707,7 @@
         <v>13500</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -3595,7 +3721,7 @@
         <v>5000</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -3609,7 +3735,7 @@
         <v>1000</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -3623,7 +3749,7 @@
         <v>975</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -3631,13 +3757,13 @@
         <v>46106</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C57" s="7">
         <v>760</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -3651,7 +3777,7 @@
         <v>55</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -3665,7 +3791,7 @@
         <v>16850</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -3679,7 +3805,7 @@
         <v>4550</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -3687,13 +3813,13 @@
         <v>46109</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C61" s="7">
         <v>7200</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -3707,7 +3833,7 @@
         <v>50000</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -3721,7 +3847,7 @@
         <v>30000</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -3735,7 +3861,7 @@
         <v>1000</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -3749,7 +3875,7 @@
         <v>5000</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -3757,13 +3883,13 @@
         <v>46113</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C66" s="7">
         <v>200</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -3777,7 +3903,7 @@
         <v>4000</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -3785,13 +3911,13 @@
         <v>46113</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68" s="7">
         <v>1440</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -3805,7 +3931,7 @@
         <v>1600</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
@@ -3819,7 +3945,7 @@
         <v>50</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
@@ -3833,7 +3959,7 @@
         <v>22900</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
@@ -3847,7 +3973,7 @@
         <v>4650</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
@@ -3861,7 +3987,7 @@
         <v>18000</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
@@ -3875,7 +4001,7 @@
         <v>72000</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
@@ -3889,7 +4015,7 @@
         <v>8000</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
@@ -3897,13 +4023,13 @@
         <v>46121</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C76" s="7">
         <v>350</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -3917,7 +4043,7 @@
         <v>220</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
@@ -3931,7 +4057,7 @@
         <v>1170</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -3939,13 +4065,13 @@
         <v>46121</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C79" s="7">
         <v>180</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
@@ -3953,13 +4079,13 @@
         <v>46121</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C80" s="7">
         <v>130</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -3973,7 +4099,7 @@
         <v>33500</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -3987,7 +4113,7 @@
         <v>1650</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
@@ -3995,13 +4121,13 @@
         <v>46125</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C83" s="7">
         <v>1600</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
@@ -4015,7 +4141,7 @@
         <v>12400</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
@@ -4029,7 +4155,7 @@
         <v>4000</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
@@ -4043,7 +4169,7 @@
         <v>30000</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
@@ -4051,13 +4177,13 @@
         <v>46128</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C87" s="7">
         <v>4060</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
@@ -4071,7 +4197,7 @@
         <v>72000</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -4085,7 +4211,7 @@
         <v>13600</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
@@ -4099,7 +4225,7 @@
         <v>100000</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
@@ -4113,7 +4239,7 @@
         <v>6000</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
@@ -4127,7 +4253,7 @@
         <v>5000</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
@@ -4135,13 +4261,13 @@
         <v>46136</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C93" s="7">
         <v>100</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
@@ -4155,7 +4281,7 @@
         <v>1290</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
@@ -4169,7 +4295,7 @@
         <v>40</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
@@ -4177,13 +4303,13 @@
         <v>46136</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C96" s="7">
         <v>4000</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
@@ -4191,13 +4317,13 @@
         <v>46136</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C97" s="7">
         <v>800</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
@@ -4211,7 +4337,7 @@
         <v>6600</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
@@ -4225,7 +4351,7 @@
         <v>1900</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
@@ -4239,7 +4365,7 @@
         <v>150</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
@@ -4253,7 +4379,7 @@
         <v>4000</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H101" s="8"/>
     </row>
@@ -4262,13 +4388,13 @@
         <v>46142</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C102" s="7">
         <v>1000</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
@@ -4282,7 +4408,7 @@
         <v>17375</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
@@ -4296,7 +4422,7 @@
         <v>9200</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
@@ -4304,13 +4430,13 @@
         <v>46146</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C105" s="7">
         <v>80000</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
@@ -4318,13 +4444,13 @@
         <v>46146</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C106" s="7">
         <v>49050</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
@@ -4332,13 +4458,13 @@
         <v>46148</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C107" s="7">
         <v>1500</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
@@ -4352,7 +4478,7 @@
         <v>5000</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
@@ -4366,7 +4492,7 @@
         <v>7000</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
@@ -4374,13 +4500,13 @@
         <v>46149</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C110" s="7">
         <v>2256</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
@@ -4394,7 +4520,7 @@
         <v>70000</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
@@ -4408,7 +4534,7 @@
         <v>1690</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
@@ -4422,7 +4548,7 @@
         <v>32275</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
@@ -4436,7 +4562,7 @@
         <v>17475</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
@@ -4450,7 +4576,7 @@
         <v>200</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
@@ -4464,7 +4590,7 @@
         <v>60000</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I116" s="8"/>
     </row>
@@ -4479,7 +4605,7 @@
         <v>50000</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
@@ -4487,239 +4613,527 @@
         <v>46151</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C118" s="7">
         <v>500</v>
       </c>
       <c r="D118" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A119" s="4">
+        <v>46151</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C119" s="7">
+        <v>50000</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A120" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C120" s="7">
+        <v>560</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A119" s="4"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="1"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A120" s="4"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="1"/>
-      <c r="I120" s="8"/>
-    </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A121" s="4"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="1"/>
+      <c r="A121" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" s="7">
+        <v>220</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I121" s="8"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A122" s="4"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="1"/>
+      <c r="A122" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" s="7">
+        <v>480</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A123" s="4"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="1"/>
+      <c r="A123" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" s="7">
+        <v>150</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A124" s="4"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="1"/>
+      <c r="A124" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124" s="7">
+        <v>250</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A125" s="4"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="1"/>
+      <c r="A125" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" s="7">
+        <v>370</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A126" s="4"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="1"/>
+      <c r="A126" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A127" s="4"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="1"/>
+      <c r="A127" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A128" s="4"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="1"/>
+      <c r="A128" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" s="7">
+        <v>12000</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A129" s="23"/>
-      <c r="B129" s="24"/>
-      <c r="C129" s="25"/>
-      <c r="D129" s="24"/>
+      <c r="A129" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C129" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A130" s="4"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="1"/>
+      <c r="A130" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C130" s="7">
+        <v>6975</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A131" s="4"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="1"/>
+      <c r="A131" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" s="7">
+        <v>35850</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A132" s="4"/>
-      <c r="B132" s="1"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="1"/>
-      <c r="F132" s="8"/>
+      <c r="A132" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="7">
+        <v>850</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A133" s="4"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="1"/>
+      <c r="A133" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" s="7">
+        <v>8400</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F133" s="8"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A134" s="4"/>
-      <c r="B134" s="1"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="1"/>
-      <c r="H134" s="8"/>
-      <c r="I134" s="8"/>
+      <c r="A134" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C134" s="7">
+        <v>25000</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A135" s="4"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="1"/>
+      <c r="A135" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="H135" s="8"/>
+      <c r="I135" s="8"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A136" s="4"/>
-      <c r="B136" s="1"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="1"/>
+      <c r="A136" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H136" s="8"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A137" s="4"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="1"/>
-      <c r="F137" s="8"/>
+      <c r="A137" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" s="7">
+        <v>12000</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A138" s="4"/>
-      <c r="B138" s="1"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="1"/>
+      <c r="A138" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C138" s="7">
+        <v>4000</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="F138" s="8"/>
-      <c r="H138" s="8"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A139" s="4"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="1"/>
+      <c r="A139" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" s="7">
+        <v>34800</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F139" s="8"/>
+      <c r="H139" s="8"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A140" s="20"/>
-      <c r="B140" s="21"/>
-      <c r="C140" s="22"/>
-      <c r="D140" s="21"/>
+      <c r="A140" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" s="7">
+        <v>1550</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A141" s="4"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="7"/>
-      <c r="D141" s="1"/>
+      <c r="A141" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C141" s="28">
+        <v>19000</v>
+      </c>
+      <c r="D141" s="27" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A142" s="4"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="7"/>
-      <c r="D142" s="1"/>
-      <c r="I142" s="8"/>
+      <c r="A142" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="7">
+        <v>1750</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A143" s="4"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="7"/>
-      <c r="D143" s="1"/>
+      <c r="A143" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C143" s="7">
+        <v>450</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I143" s="8"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A144" s="4"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="7"/>
-      <c r="D144" s="1"/>
+      <c r="A144" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A145" s="4"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="7"/>
-      <c r="D145" s="1"/>
+      <c r="A145" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="7">
+        <v>250</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A146" s="4"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="1"/>
+      <c r="A146" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C146" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A147" s="4"/>
-      <c r="B147" s="1"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="1"/>
+      <c r="A147" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C147" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A148" s="4"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="1"/>
+      <c r="A148" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="7">
+        <v>2300</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A149" s="4"/>
-      <c r="B149" s="1"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="1"/>
+      <c r="A149" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C149" s="7">
+        <v>100</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A150" s="4"/>
-      <c r="B150" s="1"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="1"/>
+      <c r="A150" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C150" s="7">
+        <v>8000</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A151" s="4"/>
-      <c r="B151" s="1"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="1"/>
+      <c r="A151" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C151" s="7">
+        <v>50000</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A152" s="4"/>
-      <c r="B152" s="1"/>
-      <c r="C152" s="7"/>
-      <c r="D152" s="1"/>
+      <c r="A152" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C152" s="7">
+        <v>200000</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A153" s="4"/>
-      <c r="B153" s="1"/>
-      <c r="C153" s="7"/>
-      <c r="D153" s="1"/>
+      <c r="A153" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C153" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A154" s="4"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="7"/>
-      <c r="D154" s="1"/>
+      <c r="A154" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C154" s="7">
+        <v>5500</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
@@ -4732,7 +5146,6 @@
       <c r="B156" s="1"/>
       <c r="C156" s="7"/>
       <c r="D156" s="1"/>
-      <c r="H156" s="8"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
@@ -4774,6 +5187,7 @@
       <c r="B162" s="1"/>
       <c r="C162" s="7"/>
       <c r="D162" s="1"/>
+      <c r="H162" s="8"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
@@ -4822,15 +5236,15 @@
       <c r="B170" s="1"/>
       <c r="C170" s="7"/>
       <c r="D170" s="1"/>
-      <c r="E170" s="26" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="1"/>
       <c r="C171" s="7"/>
       <c r="D171" s="1"/>
+      <c r="E171" s="23" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
@@ -4845,17 +5259,17 @@
       <c r="D173" s="1"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A174" s="20"/>
-      <c r="B174" s="21"/>
-      <c r="C174" s="22"/>
-      <c r="D174" s="21"/>
-      <c r="H174" s="8"/>
+      <c r="A174" s="4"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="1"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A175" s="4"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="7"/>
-      <c r="D175" s="1"/>
+      <c r="A175" s="20"/>
+      <c r="B175" s="21"/>
+      <c r="C175" s="22"/>
+      <c r="D175" s="21"/>
+      <c r="H175" s="8"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
@@ -4910,15 +5324,15 @@
       <c r="B184" s="1"/>
       <c r="C184" s="7"/>
       <c r="D184" s="1"/>
-      <c r="E184" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="4"/>
       <c r="B185" s="1"/>
       <c r="C185" s="7"/>
       <c r="D185" s="1"/>
+      <c r="E185" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
@@ -5105,13 +5519,13 @@
       <c r="B216" s="1"/>
       <c r="C216" s="7"/>
       <c r="D216" s="1"/>
-      <c r="H216" s="8"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="4"/>
       <c r="B217" s="1"/>
       <c r="C217" s="7"/>
       <c r="D217" s="1"/>
+      <c r="H217" s="8"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" s="4"/>
@@ -5168,16 +5582,16 @@
       <c r="D226" s="1"/>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A227" s="20"/>
-      <c r="B227" s="21"/>
-      <c r="C227" s="22"/>
-      <c r="D227" s="21"/>
+      <c r="A227" s="4"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="7"/>
+      <c r="D227" s="1"/>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A228" s="4"/>
-      <c r="B228" s="1"/>
-      <c r="C228" s="7"/>
-      <c r="D228" s="1"/>
+      <c r="A228" s="20"/>
+      <c r="B228" s="21"/>
+      <c r="C228" s="22"/>
+      <c r="D228" s="21"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" s="4"/>
@@ -5287,8 +5701,14 @@
       <c r="C246" s="7"/>
       <c r="D246" s="1"/>
     </row>
-    <row r="305" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F305" s="8"/>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A247" s="4"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="7"/>
+      <c r="D247" s="1"/>
+    </row>
+    <row r="306" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F306" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D42" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}"/>
@@ -5310,7 +5730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAE1F4E-AA4E-4ECE-A323-49517B1EF568}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
@@ -5348,32 +5768,32 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
@@ -5383,62 +5803,67 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -5481,7 +5906,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="18">
         <v>24300</v>
@@ -5497,7 +5922,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="18">
         <v>3640</v>
@@ -5529,7 +5954,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="18">
         <v>2310</v>
@@ -5545,7 +5970,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="18">
         <v>16740</v>
@@ -5553,7 +5978,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="18">
         <v>2260</v>
@@ -5561,7 +5986,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="18">
         <v>129050</v>
@@ -5569,7 +5994,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="18">
         <v>500</v>
@@ -5577,7 +6002,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="18">
         <v>2500</v>
